--- a/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0001T0006Z000C1N10_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0001T0006Z000C1N10_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>70.43841079687144</v>
+        <v>11.44624175449161</v>
       </c>
       <c r="D2" t="n">
-        <v>69.76310692067</v>
+        <v>11.33650487460888</v>
       </c>
       <c r="E2" t="n">
-        <v>13.26295345777855</v>
+        <v>2.155229936889014</v>
       </c>
       <c r="F2" t="n">
-        <v>13.54084356900282</v>
+        <v>2.200387079962957</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>58.72276224841291</v>
+        <v>9.542448865367097</v>
       </c>
       <c r="D3" t="n">
-        <v>57.76162636260954</v>
+        <v>9.386264283924051</v>
       </c>
       <c r="E3" t="n">
-        <v>13.26295345777855</v>
+        <v>2.155229936889014</v>
       </c>
       <c r="F3" t="n">
-        <v>13.54084356900282</v>
+        <v>2.200387079962957</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>60.218548552904</v>
+        <v>9.785514139846901</v>
       </c>
       <c r="D4" t="n">
-        <v>60.52762473485381</v>
+        <v>9.835739019413744</v>
       </c>
       <c r="E4" t="n">
-        <v>13.26295345777855</v>
+        <v>2.155229936889014</v>
       </c>
       <c r="F4" t="n">
-        <v>13.54084356900282</v>
+        <v>2.200387079962957</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>61.38946644255107</v>
+        <v>9.975788296914549</v>
       </c>
       <c r="D5" t="n">
-        <v>60.59094385192355</v>
+        <v>9.846028375937577</v>
       </c>
       <c r="E5" t="n">
-        <v>13.26295345777855</v>
+        <v>2.155229936889014</v>
       </c>
       <c r="F5" t="n">
-        <v>13.54084356900282</v>
+        <v>2.200387079962957</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>37.33134054885299</v>
+        <v>6.066342839188612</v>
       </c>
       <c r="D6" t="n">
-        <v>36.50799588145446</v>
+        <v>5.932549330736349</v>
       </c>
       <c r="E6" t="n">
-        <v>13.26295345777855</v>
+        <v>2.155229936889014</v>
       </c>
       <c r="F6" t="n">
-        <v>13.54084356900282</v>
+        <v>2.200387079962957</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>44.51192355665729</v>
+        <v>7.23318757795681</v>
       </c>
       <c r="D7" t="n">
-        <v>43.88333370221783</v>
+        <v>7.131041726610396</v>
       </c>
       <c r="E7" t="n">
-        <v>13.26295345777855</v>
+        <v>2.155229936889014</v>
       </c>
       <c r="F7" t="n">
-        <v>13.54084356900282</v>
+        <v>2.200387079962957</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>16.74811925587329</v>
+        <v>2.72156937907941</v>
       </c>
       <c r="D8" t="n">
-        <v>16.56528072675122</v>
+        <v>2.691858118097073</v>
       </c>
       <c r="E8" t="n">
-        <v>13.26295345777855</v>
+        <v>2.155229936889014</v>
       </c>
       <c r="F8" t="n">
-        <v>13.54084356900282</v>
+        <v>2.200387079962957</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>59.04996004383604</v>
+        <v>9.595618507123357</v>
       </c>
       <c r="D9" t="n">
-        <v>58.49324879429481</v>
+        <v>9.505152929072908</v>
       </c>
       <c r="E9" t="n">
-        <v>13.26295345777855</v>
+        <v>2.155229936889014</v>
       </c>
       <c r="F9" t="n">
-        <v>13.54084356900282</v>
+        <v>2.200387079962957</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>59.37089781278433</v>
+        <v>9.647770894577453</v>
       </c>
       <c r="D10" t="n">
-        <v>60.24743808745358</v>
+        <v>9.790208689211207</v>
       </c>
       <c r="E10" t="n">
-        <v>13.26295345777855</v>
+        <v>2.155229936889014</v>
       </c>
       <c r="F10" t="n">
-        <v>13.54084356900282</v>
+        <v>2.200387079962957</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>58.70313018808178</v>
+        <v>9.539258655563289</v>
       </c>
       <c r="D11" t="n">
-        <v>58.3555319206066</v>
+        <v>9.482773937098573</v>
       </c>
       <c r="E11" t="n">
-        <v>13.26295345777855</v>
+        <v>2.155229936889014</v>
       </c>
       <c r="F11" t="n">
-        <v>13.54084356900282</v>
+        <v>2.200387079962957</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>51.04968146854851</v>
+        <v>8.295573238639134</v>
       </c>
       <c r="D12" t="n">
-        <v>50.83628980550627</v>
+        <v>8.260897093394769</v>
       </c>
       <c r="E12" t="n">
-        <v>13.26295345777855</v>
+        <v>2.155229936889014</v>
       </c>
       <c r="F12" t="n">
-        <v>13.54084356900282</v>
+        <v>2.200387079962957</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>66.77707887052766</v>
+        <v>10.85127531646074</v>
       </c>
       <c r="D13" t="n">
-        <v>67.69894400320312</v>
+        <v>11.00107840052051</v>
       </c>
       <c r="E13" t="n">
-        <v>13.26295345777855</v>
+        <v>2.155229936889014</v>
       </c>
       <c r="F13" t="n">
-        <v>13.54084356900282</v>
+        <v>2.200387079962957</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>56.68214713209367</v>
+        <v>9.210848908965222</v>
       </c>
       <c r="D14" t="n">
-        <v>56.66294289073201</v>
+        <v>9.207728219743952</v>
       </c>
       <c r="E14" t="n">
-        <v>13.26295345777855</v>
+        <v>2.155229936889014</v>
       </c>
       <c r="F14" t="n">
-        <v>13.54084356900282</v>
+        <v>2.200387079962957</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>61.16239457688008</v>
+        <v>9.938889118743013</v>
       </c>
       <c r="D15" t="n">
-        <v>61.25613898288833</v>
+        <v>9.954122584719354</v>
       </c>
       <c r="E15" t="n">
-        <v>13.26295345777855</v>
+        <v>2.155229936889014</v>
       </c>
       <c r="F15" t="n">
-        <v>13.54084356900282</v>
+        <v>2.200387079962957</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>67.47058520240229</v>
+        <v>10.96397009539037</v>
       </c>
       <c r="D16" t="n">
-        <v>68.43737834803133</v>
+        <v>11.12107398155509</v>
       </c>
       <c r="E16" t="n">
-        <v>13.26295345777855</v>
+        <v>2.155229936889014</v>
       </c>
       <c r="F16" t="n">
-        <v>13.54084356900282</v>
+        <v>2.200387079962957</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>60.48316645575467</v>
+        <v>9.828514549060134</v>
       </c>
       <c r="D17" t="n">
-        <v>60.8258883957422</v>
+        <v>9.884206864308108</v>
       </c>
       <c r="E17" t="n">
-        <v>13.26295345777855</v>
+        <v>2.155229936889014</v>
       </c>
       <c r="F17" t="n">
-        <v>13.54084356900282</v>
+        <v>2.200387079962957</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>68.6899899305855</v>
+        <v>11.16212336372014</v>
       </c>
       <c r="D18" t="n">
-        <v>69.18482378905416</v>
+        <v>11.2425338657213</v>
       </c>
       <c r="E18" t="n">
-        <v>13.26295345777855</v>
+        <v>2.155229936889014</v>
       </c>
       <c r="F18" t="n">
-        <v>13.54084356900282</v>
+        <v>2.200387079962957</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>76.37010606544169</v>
+        <v>12.41014223563428</v>
       </c>
       <c r="D19" t="n">
-        <v>77.24226755305399</v>
+        <v>12.55186847737127</v>
       </c>
       <c r="E19" t="n">
-        <v>13.26295345777855</v>
+        <v>2.155229936889014</v>
       </c>
       <c r="F19" t="n">
-        <v>13.54084356900282</v>
+        <v>2.200387079962957</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
